--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="190">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -406,15 +406,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-condition.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
   </si>
   <si>
     <t>fr-lm-condition.type</t>
@@ -919,7 +910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.0859375" customWidth="true" bestFit="true"/>
@@ -2482,7 +2473,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2533,10 +2524,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2554,10 +2545,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2571,10 +2562,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2600,10 +2591,10 @@
         <v>121</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2633,10 +2624,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2654,7 +2645,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2671,10 +2662,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2697,7 +2688,7 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>135</v>
@@ -2754,7 +2745,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2766,15 +2757,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2782,7 +2773,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2797,13 +2788,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2854,10 +2845,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2866,26 +2857,26 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2897,15 +2888,17 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2942,50 +2935,50 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2997,16 +2990,16 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3044,39 +3037,39 @@
         <v>73</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3084,7 +3077,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3099,17 +3092,15 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3158,10 +3149,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3170,15 +3161,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3201,13 +3192,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3258,7 +3249,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3270,15 +3261,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3304,10 +3295,10 @@
         <v>117</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3358,7 +3349,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3375,10 +3366,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3401,13 +3392,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3437,10 +3428,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3458,7 +3449,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3475,10 +3466,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3504,10 +3495,10 @@
         <v>121</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3537,10 +3528,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3558,7 +3549,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3575,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3604,10 +3595,10 @@
         <v>121</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3637,10 +3628,10 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>177</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3658,7 +3649,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3675,10 +3666,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3689,7 +3680,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3704,10 +3695,10 @@
         <v>121</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3758,13 +3749,13 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
@@ -3775,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3804,10 +3795,10 @@
         <v>121</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3858,7 +3849,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3875,10 +3866,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3889,7 +3880,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3904,10 +3895,10 @@
         <v>121</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3937,10 +3928,10 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3958,13 +3949,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3975,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3986,10 +3977,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4001,13 +3992,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4037,10 +4028,10 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>188</v>
+        <v>73</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4058,13 +4049,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4075,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4086,10 +4077,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4101,13 +4092,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4158,118 +4149,18 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="191">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-condition.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-condition.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-condition.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-condition.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -1888,13 +1892,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1945,7 +1949,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1962,10 +1966,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1988,13 +1992,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2045,7 +2049,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2062,10 +2066,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2088,13 +2092,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2145,7 +2149,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2162,10 +2166,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2188,13 +2192,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2245,7 +2249,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2262,10 +2266,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2288,13 +2292,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2345,7 +2349,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2362,10 +2366,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2388,13 +2392,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2445,7 +2449,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2462,10 +2466,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2488,13 +2492,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2524,10 +2528,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2545,7 +2549,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2562,10 +2566,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2588,13 +2592,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2645,7 +2649,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2662,10 +2666,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2688,13 +2692,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2745,7 +2749,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2757,15 +2761,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2788,13 +2792,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2845,7 +2849,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2862,14 +2866,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -2888,16 +2892,16 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2935,19 +2939,19 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2959,15 +2963,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2990,16 +2994,16 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3049,7 +3053,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3066,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3092,13 +3096,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3149,7 +3153,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3161,15 +3165,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3192,13 +3196,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3249,7 +3253,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3266,10 +3270,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3292,13 +3296,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3349,7 +3353,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3366,10 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3392,13 +3396,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3428,10 +3432,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3449,7 +3453,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3466,10 +3470,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3492,13 +3496,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3528,10 +3532,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3549,7 +3553,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3566,10 +3570,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3592,13 +3596,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3649,7 +3653,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3666,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3692,13 +3696,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3749,7 +3753,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3766,10 +3770,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3792,13 +3796,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3849,7 +3853,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3866,10 +3870,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3892,13 +3896,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3928,10 +3932,10 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3949,7 +3953,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3966,10 +3970,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3992,13 +3996,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4049,7 +4053,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4066,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4092,13 +4096,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4149,7 +4153,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-condition.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-condition.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-condition.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-condition.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-condition.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-condition.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-condition.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-condition.header.source</t>
+    <t>fr-lm-condition.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-condition.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -560,7 +602,7 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-severite-observation-cisis</t>
   </si>
   <si>
-    <t>fr-lm-condition.status</t>
+    <t>fr-lm-condition.conditionStatus</t>
   </si>
   <si>
     <t>Statut du problème</t>
@@ -914,11 +956,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ32"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.0859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.0859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.79296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.79296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -948,7 +990,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1692,13 +1734,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1749,7 +1791,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1766,10 +1808,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1792,13 +1834,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1849,7 +1891,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1866,10 +1908,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1892,13 +1934,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1949,7 +1991,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1966,10 +2008,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1992,7 +2034,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2092,13 +2134,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2149,7 +2191,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2166,10 +2208,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2180,7 +2222,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2192,13 +2234,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2249,13 +2291,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2266,10 +2308,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2280,7 +2322,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2292,13 +2334,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2349,13 +2391,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2366,10 +2408,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2380,7 +2422,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2392,13 +2434,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2449,13 +2491,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2466,10 +2508,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2477,7 +2519,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2492,13 +2534,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2528,10 +2570,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2549,10 +2591,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2566,10 +2608,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2592,13 +2634,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2628,10 +2670,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2649,7 +2691,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2666,10 +2708,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2677,7 +2719,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2692,13 +2734,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2749,10 +2791,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2761,15 +2803,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>137</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2792,13 +2834,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2849,7 +2891,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2866,21 +2908,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2892,17 +2934,15 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2930,48 +2970,48 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>137</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2994,17 +3034,15 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3053,7 +3091,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3070,10 +3108,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3081,7 +3119,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3096,13 +3134,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3153,10 +3191,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3165,15 +3203,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3196,13 +3234,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3253,7 +3291,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3270,21 +3308,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3296,15 +3334,17 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
@@ -3341,39 +3381,39 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3381,7 +3421,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3396,15 +3436,17 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N25" s="2"/>
+      <c r="N25" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -3432,31 +3474,31 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AA25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>169</v>
-      </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3496,13 +3538,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3532,10 +3574,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3553,7 +3595,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3565,15 +3607,15 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3596,13 +3638,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3653,7 +3695,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3670,10 +3712,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3684,7 +3726,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3696,13 +3738,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3753,13 +3795,13 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
@@ -3770,10 +3812,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3784,7 +3826,7 @@
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -3796,13 +3838,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3832,10 +3874,10 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -3853,13 +3895,13 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
@@ -3870,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3896,13 +3938,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3932,10 +3974,10 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3953,7 +3995,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3970,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3981,10 +4023,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -3996,13 +4038,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4053,13 +4095,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4070,10 +4112,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4084,7 +4126,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4096,13 +4138,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4153,18 +4195,418 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="206">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -621,6 +621,10 @@
   </si>
   <si>
     <t>fr-lm-condition.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Localisation anatomique</t>
@@ -4138,13 +4142,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4212,10 +4216,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4241,10 +4245,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4295,7 +4299,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4312,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4341,10 +4345,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4374,10 +4378,10 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -4395,7 +4399,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4412,10 +4416,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4441,10 +4445,10 @@
         <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4495,7 +4499,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -4512,10 +4516,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4541,10 +4545,10 @@
         <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4595,7 +4599,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
